--- a/forDatabase.xlsx
+++ b/forDatabase.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\SoilReport\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C2B0F44C-9E59-471C-9197-CC7C5C8BA207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7185399C-6150-4EE2-A8D7-57DE8363D249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{B7B877F1-53FF-4D0A-98DC-F711C0D53CE9}"/>
   </bookViews>
@@ -36,12 +36,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="119">
   <si>
     <t>Category</t>
-  </si>
-  <si>
-    <t>Relevant for which LL</t>
   </si>
   <si>
     <t>Indicator</t>
@@ -453,7 +450,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -489,14 +486,6 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -570,12 +559,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -609,25 +597,19 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -657,14 +639,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1002,1114 +984,1054 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE255220-620A-4522-A730-51D7B8345AED}">
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="4" t="s">
+    </row>
+    <row r="2" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="16" t="s">
+      <c r="B2" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="G2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="5" t="s">
+    </row>
+    <row r="3" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="4" t="s">
+      <c r="G3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="3" t="s">
+    </row>
+    <row r="4" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="4" t="s">
+      <c r="G4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="H4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="12" t="s">
+    </row>
+    <row r="5" spans="1:8" ht="216" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="216" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="4" t="s">
+      <c r="G5" s="2"/>
+      <c r="H5" s="11"/>
+    </row>
+    <row r="6" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="12"/>
-    </row>
-    <row r="7" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="4" t="s">
+      <c r="G6" s="2"/>
+      <c r="H6" s="11"/>
+    </row>
+    <row r="7" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="12"/>
-    </row>
-    <row r="8" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="22" t="s">
+      <c r="G7" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="30" t="s">
+    </row>
+    <row r="8" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="B8" s="14"/>
+      <c r="C8" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="32" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="9" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="34" t="s">
+      <c r="A9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="31"/>
+      <c r="G9" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="H9" s="32"/>
     </row>
     <row r="10" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="33"/>
-      <c r="G10" s="3" t="s">
+      <c r="A10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="31"/>
+      <c r="G10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H10" s="34"/>
-    </row>
-    <row r="11" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="33"/>
-      <c r="G11" s="3" t="s">
+      <c r="H10" s="32"/>
+    </row>
+    <row r="11" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H11" s="34"/>
-    </row>
-    <row r="12" spans="1:8" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="4" t="s">
+      <c r="G11" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="H11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H12" s="3" t="s">
+    </row>
+    <row r="12" spans="1:8" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="14"/>
+      <c r="F12" s="29" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="16"/>
-      <c r="F13" s="32" t="s">
+      <c r="G12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="H12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="H13" s="3" t="s">
+    </row>
+    <row r="13" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="4" t="s">
+      <c r="G13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="H13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="H14" s="3" t="s">
+    </row>
+    <row r="14" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="16" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="18" t="s">
+      <c r="G14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="H14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="H15" s="3" t="s">
+    </row>
+    <row r="15" spans="1:8" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="16" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="18" t="s">
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" spans="1:8" ht="144" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-    </row>
-    <row r="17" spans="1:8" ht="144" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="29" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="F17" s="24" t="s">
+      <c r="G16" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="G17" s="25" t="s">
+      <c r="H16" s="24" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="H17" s="27" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" s="4" t="s">
+      <c r="G17" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="H17" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="H18" s="3" t="s">
+    </row>
+    <row r="18" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
+      <c r="B18" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" s="4" t="s">
+      <c r="G18" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="H18" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H19" s="5" t="s">
+    </row>
+    <row r="19" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="15"/>
+      <c r="F19" s="3" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" s="17"/>
-      <c r="F20" s="4" t="s">
+      <c r="G19" s="9"/>
+      <c r="H19" s="4"/>
+    </row>
+    <row r="20" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="15"/>
+      <c r="F20" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G20" s="10"/>
-      <c r="H20" s="5"/>
-    </row>
-    <row r="21" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="E21" s="17"/>
-      <c r="F21" s="4" t="s">
+      <c r="G20" s="9"/>
+      <c r="H20" s="4"/>
+    </row>
+    <row r="21" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="G21" s="10"/>
-      <c r="H21" s="5"/>
+      <c r="G21" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="22" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="18" t="s">
+      <c r="A22" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H22" s="4"/>
+    </row>
+    <row r="23" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E23" s="15"/>
+      <c r="F23" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="G23" s="8"/>
+      <c r="H23" s="4"/>
+    </row>
+    <row r="24" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="15"/>
+      <c r="F24" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="G24" s="8"/>
+      <c r="H24" s="7"/>
+    </row>
+    <row r="25" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="G25" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="H23" s="5"/>
-    </row>
-    <row r="24" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" s="17"/>
-      <c r="F24" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="G24" s="9"/>
-      <c r="H24" s="5"/>
-    </row>
-    <row r="25" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="E25" s="17"/>
-      <c r="F25" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="G25" s="9"/>
-      <c r="H25" s="8"/>
-    </row>
-    <row r="26" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B26" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F26" s="18" t="s">
+      <c r="H25" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="G26" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="H26" s="5" t="s">
+    </row>
+    <row r="26" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="15"/>
+      <c r="F26" s="21" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" ht="72" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="E27" s="17"/>
-      <c r="F27" s="24" t="s">
+      <c r="G26" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="G27" s="5" t="s">
+      <c r="H26" s="4"/>
+    </row>
+    <row r="27" spans="1:8" ht="144" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="H27" s="5"/>
-    </row>
-    <row r="28" spans="1:8" ht="144" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B28" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="24" t="s">
+      <c r="G27" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="H27" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="G28" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="H28" s="26" t="s">
+    </row>
+    <row r="28" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="30" t="s">
         <v>66</v>
       </c>
+      <c r="B28" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="29" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D29" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="1" t="s">
+      <c r="A29" s="30"/>
+      <c r="B29" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="30"/>
+      <c r="G29" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H29" s="3" t="s">
+      <c r="H29" s="4" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="1"/>
-      <c r="B30" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D30" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="1"/>
-      <c r="G30" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H30" s="5" t="s">
+    <row r="30" spans="1:8" ht="144" x14ac:dyDescent="0.3">
+      <c r="A30" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" s="17" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" ht="144" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B31" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" s="19" t="s">
+      <c r="G30" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="G31" s="14" t="s">
+      <c r="H30" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="H31" s="14" t="s">
+    </row>
+    <row r="31" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A31" s="30"/>
+      <c r="B31" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" s="17" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="1"/>
-      <c r="B32" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="19" t="s">
+      <c r="G31" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="G32" s="14" t="s">
+      <c r="H31" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="H32" s="14" t="s">
+    </row>
+    <row r="32" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A32" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="15"/>
+      <c r="F32" s="17" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B33" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D33" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" s="17"/>
-      <c r="F33" s="19" t="s">
+      <c r="G32" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="G33" s="14" t="s">
+      <c r="H32" s="12" t="s">
         <v>79</v>
       </c>
+    </row>
+    <row r="33" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="30"/>
+      <c r="B33" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>81</v>
+      </c>
       <c r="H33" s="13" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="1"/>
-      <c r="B34" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" s="2"/>
-      <c r="F34" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="G34" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="H34" s="14" t="s">
+    </row>
+    <row r="34" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A34" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" s="17" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B35" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E35" s="2"/>
-      <c r="F35" s="19" t="s">
+      <c r="G34" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="G35" s="14" t="s">
+      <c r="H34" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="H35" s="14" t="s">
+    </row>
+    <row r="35" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="30"/>
+      <c r="B35" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" s="17" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A36" s="1"/>
-      <c r="B36" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D36" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E36" s="2"/>
-      <c r="F36" s="19" t="s">
+      <c r="G35" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="G36" s="14" t="s">
+      <c r="H35" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="H36" s="14" t="s">
+    </row>
+    <row r="36" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" s="17" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B37" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D37" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E37" s="2"/>
-      <c r="F37" s="19" t="s">
+      <c r="G36" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="G37" s="14" t="s">
+      <c r="H36" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="H37" s="14" t="s">
+    </row>
+    <row r="37" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="30"/>
+      <c r="B37" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F37" s="17" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A38" s="1"/>
-      <c r="B38" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D38" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E38" s="2"/>
-      <c r="F38" s="19" t="s">
+      <c r="G37" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="G38" s="14" t="s">
+      <c r="H37" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="H38" s="14" t="s">
+    </row>
+    <row r="38" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" s="17" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B39" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="D39" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="E39" s="2"/>
-      <c r="F39" s="19" t="s">
+      <c r="G38" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="G39" s="14" t="s">
+      <c r="H38" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="H39" s="14" t="s">
+    </row>
+    <row r="39" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A39" s="30"/>
+      <c r="B39" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="15"/>
+      <c r="F39" s="17" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" ht="72" x14ac:dyDescent="0.3">
-      <c r="A40" s="1"/>
-      <c r="B40" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="D40" s="17"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="19" t="s">
+      <c r="G39" s="12"/>
+      <c r="H39" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="G40" s="13"/>
-      <c r="H40" s="14" t="s">
+    </row>
+    <row r="40" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="F40" s="17" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B41" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="19" t="s">
+      <c r="G40" s="12"/>
+      <c r="H40" s="13"/>
+    </row>
+    <row r="41" spans="1:8" ht="72" x14ac:dyDescent="0.3">
+      <c r="A41" s="30"/>
+      <c r="B41" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="15"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="G41" s="13"/>
-      <c r="H41" s="14"/>
-    </row>
-    <row r="42" spans="1:8" ht="72" x14ac:dyDescent="0.3">
-      <c r="A42" s="1"/>
-      <c r="B42" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="20" t="s">
+      <c r="G41" t="s">
         <v>102</v>
       </c>
-      <c r="G42" s="2" t="s">
+      <c r="H41" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="H42" s="11" t="s">
+    </row>
+    <row r="42" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" s="20"/>
+      <c r="F42" s="28" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="B43" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="23"/>
-      <c r="D43" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="E43" s="23"/>
-      <c r="F43" s="31" t="s">
+      <c r="G42" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="G43" s="28" t="s">
+      <c r="H42" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="H43" s="28" t="s">
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
         <v>107</v>
       </c>
+      <c r="F43" s="1"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="15" t="s">
+      <c r="A44" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B44" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="15"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
+      <c r="H44" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E45" s="2"/>
-      <c r="F45" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2" t="s">
+      <c r="A45" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B45" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>110</v>
       </c>
+      <c r="H45" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E46" s="2"/>
-      <c r="F46" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2" t="s">
+      <c r="A46" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B46" t="s">
+        <v>9</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="15" t="s">
+    <row r="47" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B47" t="s">
+        <v>9</v>
+      </c>
+      <c r="F47" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-    </row>
-    <row r="48" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A48" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="6" t="s">
+      <c r="G47" t="s">
         <v>114</v>
       </c>
-      <c r="G48" s="2" t="s">
+      <c r="H47" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="H48" s="11" t="s">
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B48" t="s">
+        <v>9</v>
+      </c>
+      <c r="F48" s="1" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="15" t="s">
+      <c r="A49" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B49" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49" s="25"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="25"/>
+      <c r="F49" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
+      <c r="G49" s="25"/>
+      <c r="H49" s="25"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="B50" s="28" t="s">
-        <v>10</v>
-      </c>
-      <c r="C50" s="28"/>
-      <c r="D50" s="28"/>
-      <c r="E50" s="28"/>
-      <c r="F50" s="22" t="s">
+      <c r="A50" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F50" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="G50" s="28"/>
-      <c r="H50" s="28"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="F29:F30"/>
-    <mergeCell ref="F9:F11"/>
-    <mergeCell ref="H9:H11"/>
-    <mergeCell ref="B1:E1"/>
+  <mergeCells count="10">
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="H8:H10"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A34:A35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
